--- a/docs/03_ba/dan/06_Data_Dictionary.xlsx
+++ b/docs/03_ba/dan/06_Data_Dictionary.xlsx
@@ -2,22 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_input_bundle" sheetId="1" r:id="Rf155223a7c224ab5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw_input_file" sheetId="2" r:id="R2b3fdfac729d49ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="project" sheetId="3" r:id="R0e6f9d283d4841eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch" sheetId="4" r:id="R7463d452cbd54620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parent_task" sheetId="5" r:id="R08a0d686f067408c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_reference" sheetId="6" r:id="Racee4f749dac4110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="claim_task" sheetId="7" r:id="R8472c52e3c034848"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="claim_source_map" sheetId="8" r:id="R8452da4b17e64d9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="llm_pre_score" sheetId="9" r:id="R37adc8e56ad24a22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annotation_submission" sheetId="10" r:id="R6ed63fdeedc24f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qa_review" sheetId="11" r:id="R4e5224538c42496d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rubric_version" sheetId="12" r:id="R08d507bd53074538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user_account" sheetId="13" r:id="R6da961a7b6504197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user_project_role" sheetId="14" r:id="R29107badfdc949df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_log" sheetId="15" r:id="Rfdb42cfbcbd34b10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enums" sheetId="16" r:id="R62c43c7749d74f52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pdf_bundle" sheetId="1" r:id="R490c0259fe9f4b57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pdf_file" sheetId="2" r:id="R6e9af64f51774817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pdf_parse_result" sheetId="3" r:id="R0733aef8c8a94c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="project" sheetId="4" r:id="R22475fd81b6a4a6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch" sheetId="5" r:id="R19ffe5a335ae421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parent_task" sheetId="6" r:id="R183cb896c97e43e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_reference" sheetId="7" r:id="Re8802ef9661c4810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="claim_task" sheetId="8" r:id="Rc002c5ba496a4fa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="claim_source_map" sheetId="9" r:id="R34f9986f2707405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="llm_pre_score" sheetId="10" r:id="Rb28a834f64f34f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annotation_submission" sheetId="11" r:id="R9ef8ad0e8b5d4b04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qa_review" sheetId="12" r:id="Rf31fe1f8a8624c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rubric_version" sheetId="13" r:id="R30883d5bb3814682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user_account" sheetId="14" r:id="Rf33c03bcd9d04f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="user_project_role" sheetId="15" r:id="R42ffa60a0eab4b09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_log" sheetId="16" r:id="Rdbe8b006841d4bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enums" sheetId="17" r:id="Rbb0e250a08864fa3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -49,7 +50,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="0F766E"/>
+        <x:fgColor rgb="1D4ED8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -99,7 +100,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_rawinputbundle" displayName="T_rawinputbundle" ref="A1:I10" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_pdfbundle" displayName="T_pdfbundle" ref="A1:I10" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -116,7 +117,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_annotationsubmissio" displayName="T_annotationsubmissio" ref="A1:I15" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_llmprescore" displayName="T_llmprescore" ref="A1:I15" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -133,7 +134,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="T_qareview" displayName="T_qareview" ref="A1:I7" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="T_annotationsubmission" displayName="T_annotationsubmission" ref="A1:I15" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -150,7 +151,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="T_rubricversion" displayName="T_rubricversion" ref="A1:I8" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="T_qareview" displayName="T_qareview" ref="A1:I7" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -167,7 +168,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_useraccount" displayName="T_useraccount" ref="A1:I6" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="T_rubricversion" displayName="T_rubricversion" ref="A1:I8" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -184,7 +185,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="T_userprojectrole" displayName="T_userprojectrole" ref="A1:I6" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="T_useraccount" displayName="T_useraccount" ref="A1:I6" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -201,7 +202,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="T_auditlog" displayName="T_auditlog" ref="A1:I11" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="T_userprojectrole" displayName="T_userprojectrole" ref="A1:I6" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -218,7 +219,24 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="T_enums" displayName="T_enums" ref="A1:C11" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="T_auditlog" displayName="T_auditlog" ref="A1:I11" headerRowCount="1">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="Field Name"/>
+    <x:tableColumn id="2" name="Data Type"/>
+    <x:tableColumn id="3" name="Required"/>
+    <x:tableColumn id="4" name="PK/FK"/>
+    <x:tableColumn id="5" name="Default"/>
+    <x:tableColumn id="6" name="Description"/>
+    <x:tableColumn id="7" name="Validation"/>
+    <x:tableColumn id="8" name="Example"/>
+    <x:tableColumn id="9" name="Owner"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="T_enums" displayName="T_enums" ref="A1:C12" headerRowCount="1">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Enum Name"/>
     <x:tableColumn id="2" name="Allowed Values"/>
@@ -229,7 +247,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_rawinputfile" displayName="T_rawinputfile" ref="A1:I10" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_pdffile" displayName="T_pdffile" ref="A1:I10" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -246,7 +264,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_project" displayName="T_project" ref="A1:I8" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T_pdfparseresult" displayName="T_pdfparseresult" ref="A1:I11" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -263,7 +281,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_batch" displayName="T_batch" ref="A1:I10" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T_project" displayName="T_project" ref="A1:I8" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -280,7 +298,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_parenttask" displayName="T_parenttask" ref="A1:I16" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T_batch" displayName="T_batch" ref="A1:I9" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -297,7 +315,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_sourcereference" displayName="T_sourcereference" ref="A1:I11" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T_parenttask" displayName="T_parenttask" ref="A1:I15" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -314,7 +332,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_claimtask" displayName="T_claimtask" ref="A1:I12" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T_sourcereference" displayName="T_sourcereference" ref="A1:I11" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -331,7 +349,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_claimsourcemap" displayName="T_claimsourcemap" ref="A1:I7" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="T_claimtask" displayName="T_claimtask" ref="A1:I13" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -348,7 +366,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="T_llmprescore" displayName="T_llmprescore" ref="A1:I15" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="T_claimsourcemap" displayName="T_claimsourcemap" ref="A1:I7" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Field Name"/>
     <x:tableColumn id="2" name="Data Type"/>
@@ -513,15 +531,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -558,7 +576,7 @@
         <x:v>bundle_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
-        <x:v>uuid/string</x:v>
+        <x:v>uuid</x:v>
       </x:c>
       <x:c r="C2" s="12" t="str">
         <x:v>Yes</x:v>
@@ -568,7 +586,7 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID nội bộ cho một bộ input PDF</x:v>
+        <x:v>ID của một bộ PDF input</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique, not null</x:v>
@@ -577,7 +595,7 @@
         <x:v>bundle_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -620,13 +638,13 @@
       <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Tên bundle hoặc tên bài input</x:v>
+        <x:v>Tên bundle</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
         <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>ODA_001</x:v>
+        <x:v>ODA Article 001</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
         <x:v>BA</x:v>
@@ -645,7 +663,7 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Mã bài từ portal nếu parse được</x:v>
+        <x:v>Mã bài parse từ portal PDF</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
         <x:v>If missing, generate internal code</x:v>
@@ -654,7 +672,7 @@
         <x:v>ENC_20260512_375DE786</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Parser/Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -670,21 +688,21 @@
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Tiêu đề bài</x:v>
+        <x:v>Tiêu đề bài parse từ PDF</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Can be parsed from answer PDF</x:v>
+        <x:v>Optional until parsed</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
         <x:v>Thanh toán chi phí dự án ODA...</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>status</x:v>
+        <x:v>bundle_status</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
         <x:v>enum</x:v>
@@ -700,10 +718,10 @@
         <x:v>Trạng thái bundle</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>uploaded/parsed/normalized/invalid</x:v>
+        <x:v>uploaded/parsing/parsed/parse_failed/ready_for_claim_extraction</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>normalized</x:v>
+        <x:v>parsed</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
         <x:v>Backend</x:v>
@@ -724,7 +742,7 @@
       </x:c>
       <x:c r="E8" s="12" t="str"/>
       <x:c r="F8" s="12" t="str">
-        <x:v>Người upload/preprocess</x:v>
+        <x:v>Người upload</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
         <x:v>Must exist in user_account</x:v>
@@ -787,13 +805,13 @@
         <x:v>{}</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R496b2173b6544de2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafdbc3be5ac94d3a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -802,15 +820,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -844,7 +862,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>submission_id</x:v>
+        <x:v>pre_score_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -857,13 +875,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID submission</x:v>
+        <x:v>ID pre-score</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>sub_001</x:v>
+        <x:v>pre_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -884,7 +902,7 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Claim được annotate</x:v>
+        <x:v>Claim</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
@@ -898,37 +916,35 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>annotator_id</x:v>
+        <x:v>provider</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Annotator submit</x:v>
+        <x:v>LLM provider fixed MVP</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Must exist</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>user_ann_001</x:v>
+        <x:v>fixed_provider_mvp</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>sf</x:v>
+        <x:v>model</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>decimal</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
@@ -936,46 +952,48 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Annotator score SF</x:v>
+        <x:v>Model</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>1.00</x:v>
+        <x:v>model_name</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>sc</x:v>
+        <x:v>prompt_version</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>decimal</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str"/>
+      <x:c r="E6" s="12" t="str">
+        <x:v>pre_score_v1</x:v>
+      </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Annotator score SC</x:v>
+        <x:v>Prompt version</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>0.90</x:v>
+        <x:v>pre_score_v1</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>ML/BA</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>hr</x:v>
+        <x:v>sf</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
         <x:v>decimal</x:v>
@@ -986,21 +1004,21 @@
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str"/>
       <x:c r="F7" s="12" t="str">
-        <x:v>Annotator score HR</x:v>
+        <x:v>SF score</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
         <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>1.00</x:v>
+        <x:v>0.90</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>sq</x:v>
+        <x:v>sc</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
         <x:v>decimal</x:v>
@@ -1011,21 +1029,21 @@
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str"/>
       <x:c r="F8" s="12" t="str">
-        <x:v>Annotator score SQ</x:v>
+        <x:v>SC score</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
         <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>0.90</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>rel</x:v>
+        <x:v>hr</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
         <x:v>decimal</x:v>
@@ -1036,21 +1054,21 @@
       <x:c r="D9" s="12" t="str"/>
       <x:c r="E9" s="12" t="str"/>
       <x:c r="F9" s="12" t="str">
-        <x:v>Annotator score REL</x:v>
+        <x:v>HR score</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
         <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
-        <x:v>1.00</x:v>
+        <x:v>0.95</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="str">
-        <x:v>comp</x:v>
+        <x:v>sq</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
         <x:v>decimal</x:v>
@@ -1061,21 +1079,21 @@
       <x:c r="D10" s="12" t="str"/>
       <x:c r="E10" s="12" t="str"/>
       <x:c r="F10" s="12" t="str">
-        <x:v>Annotator score COMP</x:v>
+        <x:v>SQ score</x:v>
       </x:c>
       <x:c r="G10" s="12" t="str">
         <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H10" s="12" t="str">
-        <x:v>0.85</x:v>
+        <x:v>0.90</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="str">
-        <x:v>composite_score</x:v>
+        <x:v>rel</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
         <x:v>decimal</x:v>
@@ -1086,100 +1104,98 @@
       <x:c r="D11" s="12" t="str"/>
       <x:c r="E11" s="12" t="str"/>
       <x:c r="F11" s="12" t="str">
-        <x:v>Composite score</x:v>
+        <x:v>REL score</x:v>
       </x:c>
       <x:c r="G11" s="12" t="str">
         <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H11" s="12" t="str">
-        <x:v>0.94</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="I11" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="12" t="str">
-        <x:v>annotator_note</x:v>
+        <x:v>comp</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>text</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="C12" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D12" s="12" t="str"/>
       <x:c r="E12" s="12" t="str"/>
       <x:c r="F12" s="12" t="str">
-        <x:v>Ghi chú annotator</x:v>
+        <x:v>COMP score</x:v>
       </x:c>
       <x:c r="G12" s="12" t="str">
-        <x:v>Required for inaccessible source</x:v>
+        <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H12" s="12" t="str">
-        <x:v>Nguồn xác nhận claim.</x:v>
+        <x:v>0.80</x:v>
       </x:c>
       <x:c r="I12" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="12" t="str">
-        <x:v>source_access_status</x:v>
+        <x:v>composite_score</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="D13" s="12" t="str"/>
-      <x:c r="E13" s="12" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
+      <x:c r="E13" s="12" t="str"/>
       <x:c r="F13" s="12" t="str">
-        <x:v>Trạng thái source tổng hợp</x:v>
+        <x:v>Composite</x:v>
       </x:c>
       <x:c r="G13" s="12" t="str">
-        <x:v>accessible/inaccessible/unparsed/unknown</x:v>
+        <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H13" s="12" t="str">
-        <x:v>accessible</x:v>
+        <x:v>0.89</x:v>
       </x:c>
       <x:c r="I13" s="12" t="str">
-        <x:v>Annotator</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12" t="str">
-        <x:v>status</x:v>
+        <x:v>rationale_json</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>json</x:v>
       </x:c>
       <x:c r="C14" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str"/>
       <x:c r="E14" s="12" t="str">
-        <x:v>submitted</x:v>
+        <x:v>{}</x:v>
       </x:c>
       <x:c r="F14" s="12" t="str">
-        <x:v>Submission status</x:v>
+        <x:v>Rationale</x:v>
       </x:c>
       <x:c r="G14" s="12" t="str">
-        <x:v>submitted/returned/revised</x:v>
+        <x:v>Valid JSON</x:v>
       </x:c>
       <x:c r="H14" s="12" t="str">
-        <x:v>submitted</x:v>
+        <x:v>{}</x:v>
       </x:c>
       <x:c r="I14" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>ML</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12" t="str">
-        <x:v>submitted_at</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
         <x:v>datetime</x:v>
@@ -1192,13 +1208,13 @@
         <x:v>now</x:v>
       </x:c>
       <x:c r="F15" s="12" t="str">
-        <x:v>Thời điểm submit</x:v>
+        <x:v>Created at</x:v>
       </x:c>
       <x:c r="G15" s="12" t="str">
         <x:v>ISO datetime</x:v>
       </x:c>
       <x:c r="H15" s="12" t="n">
-        <x:v>46177.375</x:v>
+        <x:v>46177.38888888889</x:v>
       </x:c>
       <x:c r="I15" s="12" t="str">
         <x:v>Backend</x:v>
@@ -1207,7 +1223,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3249c174e1a74621"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff815cb53a304646"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1216,15 +1232,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1258,7 +1274,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>qa_review_id</x:v>
+        <x:v>submission_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -1271,13 +1287,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID QA review</x:v>
+        <x:v>ID submission</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>qa_001</x:v>
+        <x:v>sub_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -1298,7 +1314,7 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Claim được QA</x:v>
+        <x:v>Claim</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
@@ -1312,7 +1328,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>qa_id</x:v>
+        <x:v>annotator_id</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>uuid</x:v>
@@ -1325,13 +1341,13 @@
       </x:c>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>QA reviewer</x:v>
+        <x:v>Annotator</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
         <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>user_qa_001</x:v>
+        <x:v>user_ann_001</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
         <x:v>Backend</x:v>
@@ -1339,10 +1355,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>decision</x:v>
+        <x:v>sf</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
@@ -1350,74 +1366,278 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Quyết định QA MVP</x:v>
+        <x:v>SF</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>approved/returned</x:v>
+        <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>approved</x:v>
+        <x:v>1.00</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>QA</x:v>
+        <x:v>Annotator</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>qa_comment</x:v>
+        <x:v>sc</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>text</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Required if returned</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Comment QA</x:v>
+        <x:v>SC</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Required when returned</x:v>
+        <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>Cần kiểm tra lại source.</x:v>
+        <x:v>0.90</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>QA</x:v>
+        <x:v>Annotator</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>reviewed_at</x:v>
+        <x:v>hr</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
+        <x:v>decimal</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="str"/>
+      <x:c r="E7" s="12" t="str"/>
+      <x:c r="F7" s="12" t="str">
+        <x:v>HR</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
+        <x:v>0.00-1.00</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="str">
+        <x:v>1.00</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="str">
+        <x:v>Annotator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>sq</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>decimal</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="str"/>
+      <x:c r="E8" s="12" t="str"/>
+      <x:c r="F8" s="12" t="str">
+        <x:v>SQ</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>0.00-1.00</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>0.90</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>Annotator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>rel</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>decimal</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="str"/>
+      <x:c r="E9" s="12" t="str"/>
+      <x:c r="F9" s="12" t="str">
+        <x:v>REL</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>0.00-1.00</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="str">
+        <x:v>1.00</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
+        <x:v>Annotator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>comp</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>decimal</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str"/>
+      <x:c r="E10" s="12" t="str"/>
+      <x:c r="F10" s="12" t="str">
+        <x:v>COMP</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>0.00-1.00</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>Annotator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>composite_score</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>decimal</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str"/>
+      <x:c r="E11" s="12" t="str"/>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Composite</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>0.00-1.00</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>source_access_status</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="str"/>
+      <x:c r="E12" s="12" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
+        <x:v>Source status</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str">
+        <x:v>source_text_parsed/inaccessible/unparsed/unknown</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="str">
+        <x:v>source_text_parsed</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="str">
+        <x:v>Annotator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>annotator_note</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="str"/>
+      <x:c r="E13" s="12" t="str"/>
+      <x:c r="F13" s="12" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str">
+        <x:v>Required for source issue</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="str">
+        <x:v>Source text trong PDF xác nhận.</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="str">
+        <x:v>Annotator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="str"/>
+      <x:c r="E14" s="12" t="str">
+        <x:v>submitted</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="str">
+        <x:v>submitted/returned/revised</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="str">
+        <x:v>submitted</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12" t="str">
+        <x:v>submitted_at</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
         <x:v>datetime</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D7" s="12" t="str"/>
-      <x:c r="E7" s="12" t="str">
+      <x:c r="C15" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="str"/>
+      <x:c r="E15" s="12" t="str">
         <x:v>now</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="str">
-        <x:v>Thời điểm QA</x:v>
-      </x:c>
-      <x:c r="G7" s="12" t="str">
+      <x:c r="F15" s="12" t="str">
+        <x:v>Submit time</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="str">
         <x:v>ISO datetime</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="n">
-        <x:v>46177.416666666664</x:v>
-      </x:c>
-      <x:c r="I7" s="12" t="str">
+      <x:c r="H15" s="12" t="n">
+        <x:v>46177.375</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="str">
         <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R607849652c814907"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6651c5c461ce4392"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1426,15 +1646,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1468,7 +1688,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>rubric_version_id</x:v>
+        <x:v>qa_review_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -1481,13 +1701,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID rubric version</x:v>
+        <x:v>ID QA review</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>rub_v1</x:v>
+        <x:v>qa_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -1495,7 +1715,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>project_id</x:v>
+        <x:v>claim_id</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
         <x:v>uuid</x:v>
@@ -1508,13 +1728,13 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Project</x:v>
+        <x:v>Claim</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>proj_001</x:v>
+        <x:v>clm_001</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
         <x:v>Backend</x:v>
@@ -1522,37 +1742,37 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>version_name</x:v>
+        <x:v>qa_id</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>uuid</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str"/>
-      <x:c r="E4" s="12" t="str">
-        <x:v>v1</x:v>
-      </x:c>
+      <x:c r="D4" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Tên version</x:v>
+        <x:v>QA user</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>v1</x:v>
+        <x:v>user_qa_001</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>dimensions_json</x:v>
+        <x:v>decision</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>json</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
@@ -1560,101 +1780,74 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>6 dimension rubric</x:v>
+        <x:v>Decision</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>Valid JSON</x:v>
+        <x:v>approved/returned</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>{"sf":{},"sc":{}}</x:v>
+        <x:v>approved</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>QA</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>weights_json</x:v>
+        <x:v>qa_comment</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>json</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Required if returned</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Trọng số</x:v>
+        <x:v>Comment</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Valid JSON</x:v>
+        <x:v>Required when returned</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>{"sf":1,"sc":1}</x:v>
+        <x:v>Cần kiểm tra mapping source.</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>QA</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>is_active</x:v>
+        <x:v>reviewed_at</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>boolean</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str">
-        <x:v>true</x:v>
+        <x:v>now</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Version active</x:v>
+        <x:v>Review time</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>true/false</x:v>
-      </x:c>
-      <x:c r="H7" s="12" t="str">
-        <x:v>true</x:v>
+        <x:v>ISO datetime</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="n">
+        <x:v>46177.416666666664</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>BA</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="12" t="str">
-        <x:v>effective_from</x:v>
-      </x:c>
-      <x:c r="B8" s="12" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="str"/>
-      <x:c r="E8" s="12" t="str">
-        <x:v>now</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="str">
-        <x:v>Hiệu lực từ</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="str">
-        <x:v>ISO datetime</x:v>
-      </x:c>
-      <x:c r="H8" s="12" t="n">
-        <x:v>46177</x:v>
-      </x:c>
-      <x:c r="I8" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28f4a9c7190348d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcafb1a7049094c84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1663,15 +1856,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1705,7 +1898,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>user_id</x:v>
+        <x:v>rubric_version_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -1718,13 +1911,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID user</x:v>
+        <x:v>ID rubric</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>user_001</x:v>
+        <x:v>rub_v1</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -1732,32 +1925,34 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>full_name</x:v>
+        <x:v>project_id</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>uuid</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str"/>
+      <x:c r="D3" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Họ tên</x:v>
+        <x:v>Project</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>Phạm Đan Kha</x:v>
+        <x:v>proj_001</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>email</x:v>
+        <x:v>version_name</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>string</x:v>
@@ -1766,78 +1961,130 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str"/>
-      <x:c r="E4" s="12" t="str"/>
+      <x:c r="E4" s="12" t="str">
+        <x:v>v1</x:v>
+      </x:c>
       <x:c r="F4" s="12" t="str">
-        <x:v>Email</x:v>
+        <x:v>Version name</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Valid email</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>example@vsf.local</x:v>
+        <x:v>v1</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>Admin</x:v>
+        <x:v>BA</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>status</x:v>
+        <x:v>dimensions_json</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>json</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str"/>
-      <x:c r="E5" s="12" t="str">
-        <x:v>active</x:v>
-      </x:c>
+      <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Trạng thái user</x:v>
+        <x:v>6 dimensions</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>active/inactive</x:v>
+        <x:v>Valid JSON</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>active</x:v>
+        <x:v>{"sf":{},"sc":{},"hr":{}}</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>Admin</x:v>
+        <x:v>BA</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>created_at</x:v>
+        <x:v>weights_json</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
+        <x:v>json</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="str"/>
+      <x:c r="E6" s="12" t="str"/>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Weights</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>Valid JSON</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>{"sf":1,"sc":1}</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="str">
+        <x:v>BA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>is_active</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>boolean</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="str"/>
+      <x:c r="E7" s="12" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="str">
+        <x:v>Active?</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
+        <x:v>true/false</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="str">
+        <x:v>BA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>effective_from</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
         <x:v>datetime</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str">
+      <x:c r="C8" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="str"/>
+      <x:c r="E8" s="12" t="str">
         <x:v>now</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="str">
-        <x:v>Ngày tạo</x:v>
-      </x:c>
-      <x:c r="G6" s="12" t="str">
+      <x:c r="F8" s="12" t="str">
+        <x:v>Effective date</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
         <x:v>ISO datetime</x:v>
       </x:c>
-      <x:c r="H6" s="12" t="n">
-        <x:v>46177.375</x:v>
-      </x:c>
-      <x:c r="I6" s="12" t="str">
-        <x:v>Backend</x:v>
+      <x:c r="H8" s="12" t="n">
+        <x:v>46177</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>BA</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d186bd9972e437e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cb0d428178745ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1846,15 +2093,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1888,7 +2135,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>user_project_role_id</x:v>
+        <x:v>user_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -1901,13 +2148,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID role assignment</x:v>
+        <x:v>ID user</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>upr_001</x:v>
+        <x:v>user_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -1915,61 +2162,57 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>user_id</x:v>
+        <x:v>full_name</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="D3" s="12" t="str"/>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>User</x:v>
+        <x:v>Họ tên</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
-        <x:v>Must exist</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>user_001</x:v>
+        <x:v>Phạm Đan Kha</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Admin</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>project_id</x:v>
+        <x:v>email</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Project</x:v>
+        <x:v>Email</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Must exist</x:v>
+        <x:v>Valid email</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>proj_001</x:v>
+        <x:v>example@vsf.local</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Admin</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>role</x:v>
+        <x:v>status</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
         <x:v>enum</x:v>
@@ -1978,15 +2221,17 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str"/>
-      <x:c r="E5" s="12" t="str"/>
+      <x:c r="E5" s="12" t="str">
+        <x:v>active</x:v>
+      </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Role trong project</x:v>
+        <x:v>Status</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>admin/annotator/qa</x:v>
+        <x:v>active/inactive</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>annotator</x:v>
+        <x:v>active</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
         <x:v>Admin</x:v>
@@ -1994,35 +2239,35 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>is_active</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>boolean</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str">
-        <x:v>true</x:v>
+        <x:v>now</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Role active</x:v>
+        <x:v>Created at</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>true/false</x:v>
-      </x:c>
-      <x:c r="H6" s="12" t="str">
-        <x:v>true</x:v>
+        <x:v>ISO datetime</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="n">
+        <x:v>46177.375</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb195da317d3445f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c5485de46314d8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2031,15 +2276,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2073,7 +2318,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>log_id</x:v>
+        <x:v>user_project_role_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -2086,13 +2331,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID log</x:v>
+        <x:v>ID role assignment</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>log_001</x:v>
+        <x:v>upr_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -2100,7 +2345,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>project_id</x:v>
+        <x:v>user_id</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
         <x:v>uuid</x:v>
@@ -2113,13 +2358,13 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Project</x:v>
+        <x:v>User</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>proj_001</x:v>
+        <x:v>user_001</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
         <x:v>Backend</x:v>
@@ -2127,26 +2372,26 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>user_id</x:v>
+        <x:v>project_id</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>uuid</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str">
         <x:v>FK</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>User thực hiện</x:v>
+        <x:v>Project</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Nullable for system</x:v>
+        <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>user_001</x:v>
+        <x:v>proj_001</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
         <x:v>Backend</x:v>
@@ -2154,7 +2399,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>entity_type</x:v>
+        <x:v>role</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
         <x:v>enum</x:v>
@@ -2165,178 +2410,49 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Loại entity</x:v>
+        <x:v>Role</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>bundle/file/parent_task/claim/source/submission/qa/export</x:v>
+        <x:v>admin/annotator/qa</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>claim</x:v>
+        <x:v>annotator</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Admin</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>entity_id</x:v>
+        <x:v>is_active</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>uuid/string</x:v>
+        <x:v>boolean</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str"/>
+      <x:c r="E6" s="12" t="str">
+        <x:v>true</x:v>
+      </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>ID entity</x:v>
+        <x:v>Active?</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>true/false</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>clm_001</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="12" t="str">
-        <x:v>action_type</x:v>
-      </x:c>
-      <x:c r="B7" s="12" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="C7" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D7" s="12" t="str"/>
-      <x:c r="E7" s="12" t="str"/>
-      <x:c r="F7" s="12" t="str">
-        <x:v>Action</x:v>
-      </x:c>
-      <x:c r="G7" s="12" t="str">
-        <x:v>Not empty</x:v>
-      </x:c>
-      <x:c r="H7" s="12" t="str">
-        <x:v>annotation_submitted</x:v>
-      </x:c>
-      <x:c r="I7" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="12" t="str">
-        <x:v>before_value</x:v>
-      </x:c>
-      <x:c r="B8" s="12" t="str">
-        <x:v>json</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="str"/>
-      <x:c r="E8" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="str">
-        <x:v>Giá trị trước</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="str">
-        <x:v>Valid JSON</x:v>
-      </x:c>
-      <x:c r="H8" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="I8" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="12" t="str">
-        <x:v>after_value</x:v>
-      </x:c>
-      <x:c r="B9" s="12" t="str">
-        <x:v>json</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="str"/>
-      <x:c r="E9" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="str">
-        <x:v>Giá trị sau</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="str">
-        <x:v>Valid JSON</x:v>
-      </x:c>
-      <x:c r="H9" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="I9" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="12" t="str">
-        <x:v>reason</x:v>
-      </x:c>
-      <x:c r="B10" s="12" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="str"/>
-      <x:c r="E10" s="12" t="str"/>
-      <x:c r="F10" s="12" t="str">
-        <x:v>Lý do nếu có</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="str">
-        <x:v>Optional</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="str">
-        <x:v>Claim text edited</x:v>
-      </x:c>
-      <x:c r="I10" s="12" t="str">
-        <x:v>User</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="12" t="str">
-        <x:v>timestamp</x:v>
-      </x:c>
-      <x:c r="B11" s="12" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="C11" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="str"/>
-      <x:c r="E11" s="12" t="str">
-        <x:v>now</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="str">
-        <x:v>Thời điểm log</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="str">
-        <x:v>ISO datetime</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="n">
-        <x:v>46177.375</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Admin</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf84d73ffb2c34444"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dd8e22cb2c6499f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2345,9 +2461,323 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Field Name</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Data Type</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>PK/FK</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Default</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Description</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Validation</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Example</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>log_id</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>uuid</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="str">
+        <x:v>PK</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="str"/>
+      <x:c r="F2" s="12" t="str">
+        <x:v>ID log</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>Unique</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="str">
+        <x:v>log_001</x:v>
+      </x:c>
+      <x:c r="I2" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12" t="str">
+        <x:v>project_id</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>uuid</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="str"/>
+      <x:c r="F3" s="12" t="str">
+        <x:v>Project</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="str">
+        <x:v>Must exist</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="str">
+        <x:v>proj_001</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>user_id</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>uuid</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="E4" s="12" t="str"/>
+      <x:c r="F4" s="12" t="str">
+        <x:v>User/system</x:v>
+      </x:c>
+      <x:c r="G4" s="12" t="str">
+        <x:v>Nullable for system</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="str">
+        <x:v>user_001</x:v>
+      </x:c>
+      <x:c r="I4" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12" t="str">
+        <x:v>entity_type</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="str"/>
+      <x:c r="E5" s="12" t="str"/>
+      <x:c r="F5" s="12" t="str">
+        <x:v>Entity type</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>pdf_bundle/pdf_file/parent_task/claim/source/submission/qa/export</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>claim</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>entity_id</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>uuid/string</x:v>
+      </x:c>
+      <x:c r="C6" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="str"/>
+      <x:c r="E6" s="12" t="str"/>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Entity ID</x:v>
+      </x:c>
+      <x:c r="G6" s="12" t="str">
+        <x:v>Not empty</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="str">
+        <x:v>clm_001</x:v>
+      </x:c>
+      <x:c r="I6" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>action_type</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="str"/>
+      <x:c r="E7" s="12" t="str"/>
+      <x:c r="F7" s="12" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="str">
+        <x:v>Not empty</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="str">
+        <x:v>annotation_submitted</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>before_value</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>json</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="str"/>
+      <x:c r="E8" s="12" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
+        <x:v>Before</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>Valid JSON</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>after_value</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>json</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="str"/>
+      <x:c r="E9" s="12" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
+        <x:v>After</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>Valid JSON</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>reason</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str"/>
+      <x:c r="E10" s="12" t="str"/>
+      <x:c r="F10" s="12" t="str">
+        <x:v>Reason</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>Optional</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>Claim text edited</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>User</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>timestamp</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str"/>
+      <x:c r="E11" s="12" t="str">
+        <x:v>now</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Timestamp</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>ISO datetime</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="n">
+        <x:v>46177.375</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7471aabf6b6479d"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2363,13 +2793,13 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>file_type</x:v>
+        <x:v>file_role</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>answer_pdf, source_ref_pdf, source_content_pdf</x:v>
       </x:c>
       <x:c r="C2" s="12" t="str">
-        <x:v>Loại file PDF input</x:v>
+        <x:v>Vai trò file PDF trong bundle</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2377,10 +2807,10 @@
         <x:v>parse_status</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>pending, parsed, unparsed, ocr_required, failed, unknown</x:v>
+        <x:v>pending, parsed, parsed_with_warnings, unparsed, ocr_required, failed, unknown</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
-        <x:v>Trạng thái parse file/source</x:v>
+        <x:v>Trạng thái parse</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2388,10 +2818,10 @@
         <x:v>bundle_status</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>uploaded, parsed, normalized, invalid</x:v>
+        <x:v>uploaded, parsing, parsed, parse_failed, ready_for_claim_extraction, invalid</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
-        <x:v>Trạng thái raw input bundle</x:v>
+        <x:v>Trạng thái bundle</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2399,7 +2829,7 @@
         <x:v>project_modality</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>text, image, audio, table, video</x:v>
+        <x:v>text_pdf, image, audio, table, video</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Modality mở rộng</x:v>
@@ -2407,74 +2837,85 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>claim_status</x:v>
+        <x:v>parent_task_status</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>claim_extracted, source_mapping_required, pre_scoring_failed, ready_for_annotation, in_annotation, submitted, qa_review, returned, approved, exported</x:v>
+        <x:v>ready_for_claim_extraction, extraction_failed, claim_extracted</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Trạng thái claim task</x:v>
+        <x:v>Trạng thái parent</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>source_access_status</x:v>
+        <x:v>claim_status</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>accessible, inaccessible, unparsed, unknown</x:v>
+        <x:v>claim_extracted, source_mapping_required, pre_scoring_failed, ready_for_annotation, in_annotation, submitted, qa_review, returned, approved, exported</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>Trạng thái truy cập/parse nguồn</x:v>
+        <x:v>Trạng thái claim</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>qa_decision</x:v>
+        <x:v>source_access_status</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>approved, returned</x:v>
+        <x:v>source_text_parsed, inaccessible, unparsed, unknown</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>Quyết định QA MVP</x:v>
+        <x:v>Trạng thái nguồn</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>project_role</x:v>
+        <x:v>qa_decision</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>admin, annotator, qa</x:v>
+        <x:v>approved, returned</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>RBAC cơ bản MVP</x:v>
+        <x:v>Quyết định QA MVP</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="str">
-        <x:v>source_tier</x:v>
+        <x:v>project_role</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Tier 1, Tier 2, Tier 3, unknown</x:v>
+        <x:v>admin, annotator, qa</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Tier nguồn</x:v>
+        <x:v>RBAC cơ bản MVP</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="str">
+        <x:v>source_tier</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>Tier 1, Tier 2, Tier 3, unknown</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Tier nguồn</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
         <x:v>mapping_method</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="str">
+      <x:c r="B12" s="12" t="str">
         <x:v>citation_marker, llm_mapping, manual_mapping</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
+      <x:c r="C12" s="12" t="str">
         <x:v>Cách map claim-source</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24fd7e8cef6b48a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50c564bdc8b94357"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2483,15 +2924,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2538,7 +2979,7 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID file</x:v>
+        <x:v>ID file PDF</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique, not null</x:v>
@@ -2568,7 +3009,7 @@
         <x:v>Bundle chứa file</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
-        <x:v>Must exist in raw_input_bundle</x:v>
+        <x:v>Must exist in pdf_bundle</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
         <x:v>bundle_001</x:v>
@@ -2579,7 +3020,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>file_type</x:v>
+        <x:v>file_role</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>enum</x:v>
@@ -2590,7 +3031,7 @@
       <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Loại file PDF</x:v>
+        <x:v>Vai trò file</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
         <x:v>answer_pdf/source_ref_pdf/source_content_pdf</x:v>
@@ -2599,7 +3040,7 @@
         <x:v>answer_pdf</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Uploader/Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2640,7 +3081,7 @@
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Đường dẫn lưu file</x:v>
+        <x:v>Đường dẫn storage</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
         <x:v>Not empty</x:v>
@@ -2654,26 +3095,26 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>parse_status</x:v>
+        <x:v>mime_type</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str">
-        <x:v>pending</x:v>
+        <x:v>application/pdf</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Trạng thái parse</x:v>
+        <x:v>MIME type</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>pending/parsed/unparsed/ocr_required/failed</x:v>
+        <x:v>Must be application/pdf</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>parsed</x:v>
+        <x:v>application/pdf</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
         <x:v>Backend</x:v>
@@ -2681,24 +3122,24 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>extracted_text_reference</x:v>
+        <x:v>file_size_bytes</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str"/>
       <x:c r="F8" s="12" t="str">
-        <x:v>Reference tới text đã extract</x:v>
+        <x:v>Kích thước file</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
-        <x:v>Optional</x:v>
+        <x:v>Within max size</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>text_ref_001</x:v>
+        <x:v>1048576</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
         <x:v>Backend</x:v>
@@ -2706,26 +3147,26 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>parse_warnings_json</x:v>
+        <x:v>parse_status</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>json</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str"/>
       <x:c r="E9" s="12" t="str">
-        <x:v>{}</x:v>
+        <x:v>pending</x:v>
       </x:c>
       <x:c r="F9" s="12" t="str">
-        <x:v>Warning khi parse</x:v>
+        <x:v>Trạng thái parse</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
-        <x:v>Valid JSON</x:v>
+        <x:v>pending/parsed/unparsed/ocr_required/failed</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
-        <x:v>{"noise_detected":true}</x:v>
+        <x:v>parsed</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
         <x:v>Backend</x:v>
@@ -2761,7 +3202,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77e671b864444cd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc28d02e7d10b49f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2770,15 +3211,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2812,7 +3253,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>project_id</x:v>
+        <x:v>parse_result_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -2825,13 +3266,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID dự án</x:v>
+        <x:v>ID parse result</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
-        <x:v>Unique, not null</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>proj_001</x:v>
+        <x:v>parse_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -2839,34 +3280,34 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>project_code</x:v>
+        <x:v>bundle_id</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>uuid</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str"/>
-      <x:c r="E3" s="12" t="str">
-        <x:v>vivipedia</x:v>
-      </x:c>
+      <x:c r="D3" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Mã dự án</x:v>
+        <x:v>Bundle được parse</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
-        <x:v>Unique per platform</x:v>
+        <x:v>Must exist in pdf_bundle</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>vivipedia</x:v>
+        <x:v>bundle_001</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>project_name</x:v>
+        <x:v>parser_version</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>string</x:v>
@@ -2875,132 +3316,211 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str"/>
-      <x:c r="E4" s="12" t="str"/>
+      <x:c r="E4" s="12" t="str">
+        <x:v>pdf_parser_v1</x:v>
+      </x:c>
       <x:c r="F4" s="12" t="str">
-        <x:v>Tên dự án</x:v>
+        <x:v>Version parser</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
         <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>Vivipedia Claim Review MVP</x:v>
+        <x:v>pdf_parser_v1</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>PO/BA</x:v>
+        <x:v>Engineering</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>modality</x:v>
+        <x:v>answer_text_raw</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str"/>
-      <x:c r="E5" s="12" t="str">
-        <x:v>text</x:v>
-      </x:c>
+      <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Loại dữ liệu chính</x:v>
+        <x:v>Text thô từ answer PDF</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>text/image/audio/table/video</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>text</x:v>
+        <x:v>RAW_TEXT</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>project_type</x:v>
+        <x:v>answer_text_normalized</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str">
-        <x:v>vivipedia_claim_review</x:v>
-      </x:c>
+      <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Loại project</x:v>
+        <x:v>Text đã clean</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Configured enum</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>vivipedia_claim_review</x:v>
+        <x:v>NORMALIZED_TEXT</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>status</x:v>
+        <x:v>metadata_extracted_json</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>json</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str">
-        <x:v>draft</x:v>
+        <x:v>{}</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Trạng thái dự án</x:v>
+        <x:v>Metadata parse được</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>draft/active/paused/archived</x:v>
+        <x:v>Valid JSON</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>active</x:v>
+        <x:v>{"article_code":"ENC_..."}</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>PO</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>created_at</x:v>
+        <x:v>source_list_extracted_json</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>datetime</x:v>
+        <x:v>json</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
+        <x:v>Danh sách source parse từ Ref PDF</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>Valid JSON, at least 1 source</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>[{"source_order":1}]</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>Parser</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>parse_warnings_json</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>json</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="str"/>
+      <x:c r="E9" s="12" t="str">
+        <x:v>[]</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
+        <x:v>Warnings parse</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>Valid JSON</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="str">
+        <x:v>[{"warning_code":"SOURCE_URL_MISSING"}]</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
+        <x:v>Parser</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>parse_status</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str"/>
+      <x:c r="E10" s="12" t="str">
+        <x:v>pending</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="str">
+        <x:v>Trạng thái parse tổng</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>parsed/parsed_with_warnings/failed</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>parsed_with_warnings</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>parsed_at</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str"/>
+      <x:c r="E11" s="12" t="str">
         <x:v>now</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="str">
-        <x:v>Ngày tạo</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="str">
+      <x:c r="F11" s="12" t="str">
+        <x:v>Thời điểm parse</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
         <x:v>ISO datetime</x:v>
       </x:c>
-      <x:c r="H8" s="12" t="n">
-        <x:v>46177.375</x:v>
-      </x:c>
-      <x:c r="I8" s="12" t="str">
+      <x:c r="H11" s="12" t="n">
+        <x:v>46177.381944444445</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
         <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77a81f6bb3d94a15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd75a7b3c328548aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3009,15 +3529,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3051,7 +3571,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>batch_id</x:v>
+        <x:v>project_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -3064,13 +3584,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID batch</x:v>
+        <x:v>ID dự án</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
-        <x:v>Unique, not null</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>batch_001</x:v>
+        <x:v>proj_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -3078,34 +3598,34 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>project_id</x:v>
+        <x:v>project_code</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="str"/>
+      <x:c r="D3" s="12" t="str"/>
+      <x:c r="E3" s="12" t="str">
+        <x:v>vivipedia</x:v>
+      </x:c>
       <x:c r="F3" s="12" t="str">
-        <x:v>Dự án chứa batch</x:v>
+        <x:v>Mã dự án</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
-        <x:v>Must exist in project</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>proj_001</x:v>
+        <x:v>vivipedia</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>BA/Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>batch_name</x:v>
+        <x:v>project_name</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>string</x:v>
@@ -3116,21 +3636,21 @@
       <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Tên batch</x:v>
+        <x:v>Tên dự án</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
         <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>MVP Sample Batch 01</x:v>
+        <x:v>Vivipedia PDF Claim Review MVP</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>PO/BA</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>import_mode</x:v>
+        <x:v>modality</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
         <x:v>enum</x:v>
@@ -3140,24 +3660,24 @@
       </x:c>
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str">
-        <x:v>normalized_csv</x:v>
+        <x:v>text_pdf</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Cách import</x:v>
+        <x:v>Loại input chính</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>pdf_bundle/normalized_csv/normalized_json</x:v>
+        <x:v>text_pdf/image/audio/table</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>normalized_csv</x:v>
+        <x:v>text_pdf</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>BA/Dev</x:v>
+        <x:v>BA</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>import_format</x:v>
+        <x:v>project_type</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
         <x:v>enum</x:v>
@@ -3167,133 +3687,79 @@
       </x:c>
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str">
-        <x:v>csv</x:v>
+        <x:v>vivipedia_pdf_claim_review</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Format import</x:v>
+        <x:v>Loại project</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>csv/json/pdf_bundle</x:v>
+        <x:v>Configured enum</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>csv</x:v>
+        <x:v>vivipedia_pdf_claim_review</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>BA/Dev</x:v>
+        <x:v>BA</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>total_bundles</x:v>
+        <x:v>status</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>integer</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str">
-        <x:v>0</x:v>
+        <x:v>active</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Tổng bundle/row input</x:v>
+        <x:v>Trạng thái</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>&gt;=0</x:v>
+        <x:v>draft/active/paused/archived</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>2</x:v>
+        <x:v>active</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>PO</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>valid_bundles</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>integer</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str">
-        <x:v>0</x:v>
+        <x:v>now</x:v>
       </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Số bundle hợp lệ</x:v>
+        <x:v>Ngày tạo</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
-        <x:v>&gt;=0</x:v>
-      </x:c>
-      <x:c r="H8" s="12" t="str">
-        <x:v>2</x:v>
+        <x:v>ISO datetime</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="n">
+        <x:v>46177.375</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="12" t="str">
-        <x:v>invalid_bundles</x:v>
-      </x:c>
-      <x:c r="B9" s="12" t="str">
-        <x:v>integer</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="str"/>
-      <x:c r="E9" s="12" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="str">
-        <x:v>Số bundle lỗi</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="str">
-        <x:v>&gt;=0</x:v>
-      </x:c>
-      <x:c r="H9" s="12" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="12" t="str">
-        <x:v>imported_at</x:v>
-      </x:c>
-      <x:c r="B10" s="12" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="str"/>
-      <x:c r="E10" s="12" t="str">
-        <x:v>now</x:v>
-      </x:c>
-      <x:c r="F10" s="12" t="str">
-        <x:v>Thời điểm import</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="str">
-        <x:v>ISO datetime</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="n">
-        <x:v>46177.375</x:v>
-      </x:c>
-      <x:c r="I10" s="12" t="str">
         <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8570c41e2c9d40bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reda96fe523944e00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3302,15 +3768,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3344,7 +3810,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>parent_task_id</x:v>
+        <x:v>batch_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -3357,13 +3823,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID parent task</x:v>
+        <x:v>ID batch upload</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
-        <x:v>Unique, not null</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>pt_001</x:v>
+        <x:v>batch_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -3371,7 +3837,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>bundle_id</x:v>
+        <x:v>project_id</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
         <x:v>uuid</x:v>
@@ -3384,13 +3850,13 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Bundle PDF gốc</x:v>
+        <x:v>Dự án chứa batch</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
-        <x:v>Must exist in raw_input_bundle</x:v>
+        <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>bundle_001</x:v>
+        <x:v>proj_001</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
         <x:v>Backend</x:v>
@@ -3398,341 +3864,168 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>batch_id</x:v>
+        <x:v>batch_name</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Batch chứa task</x:v>
+        <x:v>Tên batch</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Must exist in batch</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>batch_001</x:v>
+        <x:v>MVP PDF Batch 01</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>BA</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>article_code</x:v>
+        <x:v>import_type</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str"/>
-      <x:c r="E5" s="12" t="str"/>
+      <x:c r="E5" s="12" t="str">
+        <x:v>pdf_bundle</x:v>
+      </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Mã bài portal hoặc internal</x:v>
+        <x:v>Loại import</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>pdf_bundle</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>ENC_20260512_375DE786</x:v>
+        <x:v>pdf_bundle</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>BA/Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>title</x:v>
+        <x:v>total_bundles</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str"/>
+      <x:c r="E6" s="12" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Tiêu đề bài</x:v>
+        <x:v>Tổng bundle</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>&gt;=0</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>Thanh toán chi phí dự án ODA...</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>category</x:v>
+        <x:v>valid_bundles</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str"/>
-      <x:c r="E7" s="12" t="str"/>
+      <x:c r="E7" s="12" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Danh mục</x:v>
+        <x:v>Bundle valid</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>Optional</x:v>
+        <x:v>&gt;=0</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>Hành chính</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>tier</x:v>
+        <x:v>invalid_bundles</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D8" s="12" t="str"/>
-      <x:c r="E8" s="12" t="str"/>
+      <x:c r="E8" s="12" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F8" s="12" t="str">
-        <x:v>Tầng bài</x:v>
+        <x:v>Bundle invalid</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
-        <x:v>Optional</x:v>
+        <x:v>&gt;=0</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>T3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>confidence_score</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>decimal</x:v>
+        <x:v>datetime</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D9" s="12" t="str"/>
-      <x:c r="E9" s="12" t="str"/>
+      <x:c r="E9" s="12" t="str">
+        <x:v>now</x:v>
+      </x:c>
       <x:c r="F9" s="12" t="str">
-        <x:v>Confidence score từ portal</x:v>
+        <x:v>Thời điểm tạo</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
-        <x:v>0.00-1.00 if present</x:v>
-      </x:c>
-      <x:c r="H9" s="12" t="str">
-        <x:v>0.10</x:v>
+        <x:v>ISO datetime</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="n">
+        <x:v>46177.375</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
-        <x:v>BA</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="12" t="str">
-        <x:v>created_date</x:v>
-      </x:c>
-      <x:c r="B10" s="12" t="str">
-        <x:v>date</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="str"/>
-      <x:c r="E10" s="12" t="str"/>
-      <x:c r="F10" s="12" t="str">
-        <x:v>Ngày tạo từ portal</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="str">
-        <x:v>Valid date if present</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="str">
-        <x:v>2026-05-12</x:v>
-      </x:c>
-      <x:c r="I10" s="12" t="str">
-        <x:v>BA</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="12" t="str">
-        <x:v>answer_text_raw</x:v>
-      </x:c>
-      <x:c r="B11" s="12" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="C11" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="str"/>
-      <x:c r="E11" s="12" t="str"/>
-      <x:c r="F11" s="12" t="str">
-        <x:v>Text parse thô từ PDF</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="str">
-        <x:v>Not empty</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="str">
-        <x:v>RAW_TEXT_FROM_PDF</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="str">
-        <x:v>BA/Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="12" t="str">
-        <x:v>answer_text_normalized</x:v>
-      </x:c>
-      <x:c r="B12" s="12" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="C12" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="str"/>
-      <x:c r="E12" s="12" t="str"/>
-      <x:c r="F12" s="12" t="str">
-        <x:v>Text đã clean để đưa vào extraction</x:v>
-      </x:c>
-      <x:c r="G12" s="12" t="str">
-        <x:v>Not empty</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="str">
-        <x:v>NORMALIZED_ANSWER_TEXT</x:v>
-      </x:c>
-      <x:c r="I12" s="12" t="str">
-        <x:v>BA/Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="12" t="str">
-        <x:v>answer_reference</x:v>
-      </x:c>
-      <x:c r="B13" s="12" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="C13" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="str"/>
-      <x:c r="E13" s="12" t="str"/>
-      <x:c r="F13" s="12" t="str">
-        <x:v>Reference tới full answer</x:v>
-      </x:c>
-      <x:c r="G13" s="12" t="str">
-        <x:v>Not empty</x:v>
-      </x:c>
-      <x:c r="H13" s="12" t="str">
-        <x:v>answer_ref_001</x:v>
-      </x:c>
-      <x:c r="I13" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="12" t="str">
-        <x:v>status</x:v>
-      </x:c>
-      <x:c r="B14" s="12" t="str">
-        <x:v>enum</x:v>
-      </x:c>
-      <x:c r="C14" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="str"/>
-      <x:c r="E14" s="12" t="str">
-        <x:v>imported</x:v>
-      </x:c>
-      <x:c r="F14" s="12" t="str">
-        <x:v>Trạng thái parent task</x:v>
-      </x:c>
-      <x:c r="G14" s="12" t="str">
-        <x:v>imported/extraction_failed/claim_extracted/...</x:v>
-      </x:c>
-      <x:c r="H14" s="12" t="str">
-        <x:v>claim_extracted</x:v>
-      </x:c>
-      <x:c r="I14" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="12" t="str">
-        <x:v>total_claims</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="str">
-        <x:v>integer</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="str"/>
-      <x:c r="E15" s="12" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="str">
-        <x:v>Số claim sinh ra</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="str">
-        <x:v>&gt;=0</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="str">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="12" t="str">
-        <x:v>metadata_json</x:v>
-      </x:c>
-      <x:c r="B16" s="12" t="str">
-        <x:v>json</x:v>
-      </x:c>
-      <x:c r="C16" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="str"/>
-      <x:c r="E16" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="F16" s="12" t="str">
-        <x:v>Metadata phụ</x:v>
-      </x:c>
-      <x:c r="G16" s="12" t="str">
-        <x:v>Valid JSON</x:v>
-      </x:c>
-      <x:c r="H16" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="I16" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11023b32f9334313"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R198135bca9524c45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3741,15 +4034,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3783,7 +4076,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>source_id</x:v>
+        <x:v>parent_task_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -3796,13 +4089,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID source</x:v>
+        <x:v>ID parent task</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
-        <x:v>Unique, not null</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>src_001</x:v>
+        <x:v>pt_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -3810,7 +4103,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>parent_task_id</x:v>
+        <x:v>bundle_id</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
         <x:v>uuid</x:v>
@@ -3823,13 +4116,13 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Parent task chứa source list</x:v>
+        <x:v>PDF bundle gốc</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>pt_001</x:v>
+        <x:v>bundle_001</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
         <x:v>Backend</x:v>
@@ -3837,35 +4130,37 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>source_order</x:v>
+        <x:v>batch_id</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>integer</x:v>
+        <x:v>uuid</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str"/>
+      <x:c r="D4" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Số thứ tự source</x:v>
+        <x:v>Batch</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Unique per parent, &gt;=1</x:v>
+        <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>1</x:v>
+        <x:v>batch_001</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>source_title</x:v>
+        <x:v>article_code</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
@@ -3873,51 +4168,49 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Tiêu đề nguồn</x:v>
+        <x:v>Mã bài</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
         <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>Thông tư số 66/2023/TT-BTC</x:v>
+        <x:v>ENC_20260512_375DE786</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>source_tier</x:v>
+        <x:v>title</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
+      <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Tier nguồn</x:v>
+        <x:v>Tiêu đề</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Tier 1/Tier 2/Tier 3/unknown</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>Tier 1</x:v>
+        <x:v>Thanh toán chi phí dự án ODA...</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>BA</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>source_url</x:v>
+        <x:v>category</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>text</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>No</x:v>
@@ -3925,49 +4218,49 @@
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str"/>
       <x:c r="F7" s="12" t="str">
-        <x:v>URL nếu parse được</x:v>
+        <x:v>Danh mục</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>http/https if present</x:v>
-      </x:c>
-      <x:c r="H7" s="12"/>
+        <x:v>Optional</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="str">
+        <x:v>Hành chính</x:v>
+      </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>source_file_id</x:v>
+        <x:v>tier</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str"/>
       <x:c r="F8" s="12" t="str">
-        <x:v>File PDF nội dung nguồn</x:v>
+        <x:v>Tầng</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
-        <x:v>Must exist if present</x:v>
+        <x:v>Optional</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>file_003</x:v>
+        <x:v>T3</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>source_text_reference</x:v>
+        <x:v>confidence_score</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
         <x:v>No</x:v>
@@ -3975,76 +4268,178 @@
       <x:c r="D9" s="12" t="str"/>
       <x:c r="E9" s="12" t="str"/>
       <x:c r="F9" s="12" t="str">
-        <x:v>Reference tới extracted source text</x:v>
+        <x:v>Confidence score</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
-        <x:v>Optional</x:v>
+        <x:v>0.00-1.00 if present</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
-        <x:v>source_text_001</x:v>
+        <x:v>0.10</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="str">
-        <x:v>access_status</x:v>
+        <x:v>created_date</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>date</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str"/>
-      <x:c r="E10" s="12" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
+      <x:c r="E10" s="12" t="str"/>
       <x:c r="F10" s="12" t="str">
-        <x:v>Trạng thái truy cập</x:v>
+        <x:v>Ngày tạo từ portal</x:v>
       </x:c>
       <x:c r="G10" s="12" t="str">
-        <x:v>accessible/inaccessible/unparsed/unknown</x:v>
+        <x:v>Valid date</x:v>
       </x:c>
       <x:c r="H10" s="12" t="str">
-        <x:v>accessible</x:v>
+        <x:v>2026-05-12</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>Annotator/Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="str">
-        <x:v>parse_status</x:v>
+        <x:v>answer_text_normalized</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str"/>
+      <x:c r="E11" s="12" t="str"/>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Text dùng cho claim extraction</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>Not empty</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>NORMALIZED_TEXT</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>Parser</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>answer_reference</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="str"/>
+      <x:c r="E12" s="12" t="str"/>
+      <x:c r="F12" s="12" t="str">
+        <x:v>Reference full answer</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str">
+        <x:v>Not empty</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="str">
+        <x:v>answer_ref_001</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
         <x:v>enum</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="str"/>
-      <x:c r="E11" s="12" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="str">
-        <x:v>Trạng thái parse source text</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="str">
-        <x:v>parsed/unparsed/ocr_required/unknown</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="str">
-        <x:v>parsed</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="str">
+      <x:c r="C13" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="str"/>
+      <x:c r="E13" s="12" t="str">
+        <x:v>ready_for_claim_extraction</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="str">
+        <x:v>Trạng thái task</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str">
+        <x:v>see enums</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="str">
+        <x:v>ready_for_claim_extraction</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12" t="str">
+        <x:v>total_claims</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>integer</x:v>
+      </x:c>
+      <x:c r="C14" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="str"/>
+      <x:c r="E14" s="12" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
+        <x:v>Số claim</x:v>
+      </x:c>
+      <x:c r="G14" s="12" t="str">
+        <x:v>&gt;=0</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I14" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12" t="str">
+        <x:v>metadata_json</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
+        <x:v>json</x:v>
+      </x:c>
+      <x:c r="C15" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="str"/>
+      <x:c r="E15" s="12" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
+        <x:v>Metadata phụ</x:v>
+      </x:c>
+      <x:c r="G15" s="12" t="str">
+        <x:v>Valid JSON</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="str">
+        <x:v>{}</x:v>
+      </x:c>
+      <x:c r="I15" s="12" t="str">
         <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb31f1effe7354f9b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ea498f535b14400"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4053,15 +4448,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4095,7 +4490,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>claim_id</x:v>
+        <x:v>source_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -4108,13 +4503,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID claim</x:v>
+        <x:v>ID source</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
-        <x:v>Unique, not null</x:v>
+        <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>clm_001</x:v>
+        <x:v>src_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -4135,7 +4530,7 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Parent task chứa claim</x:v>
+        <x:v>Parent task</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
@@ -4149,7 +4544,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>claim_order</x:v>
+        <x:v>source_order</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>integer</x:v>
@@ -4160,21 +4555,21 @@
       <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Thứ tự claim</x:v>
+        <x:v>Thứ tự source</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>&gt;=1 unique per parent</x:v>
+        <x:v>Unique per parent, &gt;=1</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>claim_text_original</x:v>
+        <x:v>source_title</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
         <x:v>text</x:v>
@@ -4185,49 +4580,51 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Claim do extraction sinh</x:v>
+        <x:v>Tiêu đề source</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
         <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>Thông tư 66 có hiệu lực từ...</x:v>
+        <x:v>Thông tư số 66/2023/TT-BTC</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>LLM/Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>claim_text_final</x:v>
+        <x:v>source_tier</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>text</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>No</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
-      <x:c r="E6" s="12" t="str"/>
+      <x:c r="E6" s="12" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>Claim sau khi annotator/QA sửa</x:v>
+        <x:v>Tier source</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Optional</x:v>
+        <x:v>Tier 1/Tier 2/Tier 3/unknown</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>Thông tư 66/2023/TT-BTC có hiệu lực...</x:v>
+        <x:v>Tier 1</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>Annotator/QA</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>citation_markers</x:v>
+        <x:v>source_url</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>No</x:v>
@@ -4235,40 +4632,38 @@
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str"/>
       <x:c r="F7" s="12" t="str">
-        <x:v>Citation markers gốc</x:v>
+        <x:v>URL nếu parse được</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>Format like [1];[3]</x:v>
-      </x:c>
-      <x:c r="H7" s="12" t="str">
-        <x:v>[1];[3]</x:v>
-      </x:c>
+        <x:v>http/https if present</x:v>
+      </x:c>
+      <x:c r="H7" s="12"/>
       <x:c r="I7" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>status</x:v>
+        <x:v>source_file_id</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>uuid</x:v>
       </x:c>
       <x:c r="C8" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="str"/>
-      <x:c r="E8" s="12" t="str">
-        <x:v>claim_extracted</x:v>
-      </x:c>
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="E8" s="12" t="str"/>
       <x:c r="F8" s="12" t="str">
-        <x:v>Trạng thái claim</x:v>
+        <x:v>PDF content source</x:v>
       </x:c>
       <x:c r="G8" s="12" t="str">
-        <x:v>see enums sheet</x:v>
+        <x:v>Must exist if present</x:v>
       </x:c>
       <x:c r="H8" s="12" t="str">
-        <x:v>ready_for_annotation</x:v>
+        <x:v>file_003</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
         <x:v>Backend</x:v>
@@ -4276,112 +4671,87 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>assigned_annotator_id</x:v>
+        <x:v>source_text_extract</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="D9" s="12" t="str"/>
       <x:c r="E9" s="12" t="str"/>
       <x:c r="F9" s="12" t="str">
-        <x:v>Annotator được giao</x:v>
+        <x:v>Text parse từ source PDF</x:v>
       </x:c>
       <x:c r="G9" s="12" t="str">
-        <x:v>Must exist if assigned</x:v>
+        <x:v>Optional</x:v>
       </x:c>
       <x:c r="H9" s="12" t="str">
-        <x:v>user_annotator_001</x:v>
+        <x:v>THÔNG TƯ...</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="12" t="str">
-        <x:v>rubric_version</x:v>
+        <x:v>source_parse_status</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str"/>
       <x:c r="E10" s="12" t="str">
-        <x:v>v1</x:v>
+        <x:v>unknown</x:v>
       </x:c>
       <x:c r="F10" s="12" t="str">
-        <x:v>Rubric version</x:v>
+        <x:v>Parse status</x:v>
       </x:c>
       <x:c r="G10" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>parsed/unparsed/ocr_required/unknown</x:v>
       </x:c>
       <x:c r="H10" s="12" t="str">
-        <x:v>v1</x:v>
+        <x:v>parsed</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>BA/Backend</x:v>
+        <x:v>Parser</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="12" t="str">
-        <x:v>submitted_at</x:v>
+        <x:v>access_status</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>datetime</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str"/>
-      <x:c r="E11" s="12" t="str"/>
+      <x:c r="E11" s="12" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
       <x:c r="F11" s="12" t="str">
-        <x:v>Thời điểm submit</x:v>
+        <x:v>Access/status tổng</x:v>
       </x:c>
       <x:c r="G11" s="12" t="str">
-        <x:v>ISO datetime</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="n">
-        <x:v>46177.375</x:v>
+        <x:v>source_text_parsed/inaccessible/unparsed/unknown</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>source_text_parsed</x:v>
       </x:c>
       <x:c r="I11" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="12" t="str">
-        <x:v>approved_at</x:v>
-      </x:c>
-      <x:c r="B12" s="12" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="C12" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="str"/>
-      <x:c r="E12" s="12" t="str"/>
-      <x:c r="F12" s="12" t="str">
-        <x:v>Thời điểm approved</x:v>
-      </x:c>
-      <x:c r="G12" s="12" t="str">
-        <x:v>ISO datetime</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="n">
-        <x:v>46177.416666666664</x:v>
-      </x:c>
-      <x:c r="I12" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Annotator/Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9c4841abc4f4e93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ec7b81f2f084bed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4390,15 +4760,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4432,7 +4802,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>claim_source_map_id</x:v>
+        <x:v>claim_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -4445,13 +4815,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID mapping</x:v>
+        <x:v>ID claim</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>csm_001</x:v>
+        <x:v>clm_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -4459,7 +4829,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>claim_id</x:v>
+        <x:v>parent_task_id</x:v>
       </x:c>
       <x:c r="B3" s="12" t="str">
         <x:v>uuid</x:v>
@@ -4472,13 +4842,13 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Claim được map</x:v>
+        <x:v>Parent task</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H3" s="12" t="str">
-        <x:v>clm_001</x:v>
+        <x:v>pt_001</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
         <x:v>Backend</x:v>
@@ -4486,26 +4856,24 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>source_id</x:v>
+        <x:v>claim_order</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>uuid</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
-        <x:v>FK</x:v>
-      </x:c>
+      <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>Source được map</x:v>
+        <x:v>Thứ tự claim</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Must exist</x:v>
+        <x:v>&gt;=1 unique per parent</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>src_001</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
         <x:v>Backend</x:v>
@@ -4513,87 +4881,239 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>mapping_method</x:v>
+        <x:v>section_name</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>enum</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str"/>
-      <x:c r="E5" s="12" t="str">
-        <x:v>citation_marker</x:v>
-      </x:c>
+      <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str">
-        <x:v>Cách map</x:v>
+        <x:v>Section chứa claim</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>citation_marker/llm_mapping/manual_mapping</x:v>
+        <x:v>Optional</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>citation_marker</x:v>
+        <x:v>Tóm tắt</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>Parser/LLM</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>mapping_confidence</x:v>
+        <x:v>claim_text_original</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>decimal</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Độ tin cậy mapping</x:v>
+        <x:v>Claim sinh ra</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
+        <x:v>Not empty</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>0.90</x:v>
+        <x:v>Thông tư 66 có hiệu lực...</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>Backend</x:v>
+        <x:v>LLM</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>is_primary_source</x:v>
+        <x:v>claim_text_final</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>boolean</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str"/>
-      <x:c r="E7" s="12" t="str">
-        <x:v>false</x:v>
-      </x:c>
+      <x:c r="E7" s="12" t="str"/>
       <x:c r="F7" s="12" t="str">
-        <x:v>Có phải source chính không</x:v>
+        <x:v>Claim sửa bởi annotator/QA</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>true/false</x:v>
+        <x:v>Optional</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>true</x:v>
+        <x:v>Thông tư 66/2023...</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>Backend/Annotator</x:v>
+        <x:v>Annotator/QA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>citation_markers</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C8" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="str"/>
+      <x:c r="E8" s="12" t="str"/>
+      <x:c r="F8" s="12" t="str">
+        <x:v>Markers gốc</x:v>
+      </x:c>
+      <x:c r="G8" s="12" t="str">
+        <x:v>Format [1];[3]</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="str">
+        <x:v>[1]</x:v>
+      </x:c>
+      <x:c r="I8" s="12" t="str">
+        <x:v>LLM/Parser</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>enum</x:v>
+      </x:c>
+      <x:c r="C9" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="str"/>
+      <x:c r="E9" s="12" t="str">
+        <x:v>claim_extracted</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
+        <x:v>Trạng thái claim</x:v>
+      </x:c>
+      <x:c r="G9" s="12" t="str">
+        <x:v>see enums</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="str">
+        <x:v>ready_for_annotation</x:v>
+      </x:c>
+      <x:c r="I9" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>assigned_annotator_id</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>uuid</x:v>
+      </x:c>
+      <x:c r="C10" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
+      <x:c r="E10" s="12" t="str"/>
+      <x:c r="F10" s="12" t="str">
+        <x:v>Annotator</x:v>
+      </x:c>
+      <x:c r="G10" s="12" t="str">
+        <x:v>Must exist if assigned</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="str">
+        <x:v>user_ann_001</x:v>
+      </x:c>
+      <x:c r="I10" s="12" t="str">
+        <x:v>Admin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>rubric_version</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C11" s="12" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="str"/>
+      <x:c r="E11" s="12" t="str">
+        <x:v>v1</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Rubric version</x:v>
+      </x:c>
+      <x:c r="G11" s="12" t="str">
+        <x:v>Not empty</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="str">
+        <x:v>v1</x:v>
+      </x:c>
+      <x:c r="I11" s="12" t="str">
+        <x:v>BA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>submitted_at</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="C12" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="str"/>
+      <x:c r="E12" s="12" t="str"/>
+      <x:c r="F12" s="12" t="str">
+        <x:v>Submit time</x:v>
+      </x:c>
+      <x:c r="G12" s="12" t="str">
+        <x:v>ISO datetime</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="n">
+        <x:v>46177.375</x:v>
+      </x:c>
+      <x:c r="I12" s="12" t="str">
+        <x:v>Backend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>approved_at</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
+        <x:v>datetime</x:v>
+      </x:c>
+      <x:c r="C13" s="12" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="str"/>
+      <x:c r="E13" s="12" t="str"/>
+      <x:c r="F13" s="12" t="str">
+        <x:v>Approve time</x:v>
+      </x:c>
+      <x:c r="G13" s="12" t="str">
+        <x:v>ISO datetime</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="n">
+        <x:v>46177.416666666664</x:v>
+      </x:c>
+      <x:c r="I13" s="12" t="str">
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86c5e48753f948f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84cb60d4f16d4391"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4602,15 +5122,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="36" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4644,7 +5164,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="12" t="str">
-        <x:v>pre_score_id</x:v>
+        <x:v>claim_source_map_id</x:v>
       </x:c>
       <x:c r="B2" s="12" t="str">
         <x:v>uuid</x:v>
@@ -4657,13 +5177,13 @@
       </x:c>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str">
-        <x:v>ID pre-score</x:v>
+        <x:v>ID mapping</x:v>
       </x:c>
       <x:c r="G2" s="12" t="str">
         <x:v>Unique</x:v>
       </x:c>
       <x:c r="H2" s="12" t="str">
-        <x:v>pre_001</x:v>
+        <x:v>csm_001</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
         <x:v>Backend</x:v>
@@ -4684,7 +5204,7 @@
       </x:c>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str">
-        <x:v>Claim được chấm</x:v>
+        <x:v>Claim</x:v>
       </x:c>
       <x:c r="G3" s="12" t="str">
         <x:v>Must exist</x:v>
@@ -4698,312 +5218,114 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>provider</x:v>
+        <x:v>source_id</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>uuid</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str"/>
+      <x:c r="D4" s="12" t="str">
+        <x:v>FK</x:v>
+      </x:c>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str">
-        <x:v>LLM provider MVP</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="G4" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>Must exist</x:v>
       </x:c>
       <x:c r="H4" s="12" t="str">
-        <x:v>fixed_provider_mvp</x:v>
+        <x:v>src_001</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>ML</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>model</x:v>
+        <x:v>mapping_method</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>enum</x:v>
       </x:c>
       <x:c r="C5" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D5" s="12" t="str"/>
-      <x:c r="E5" s="12" t="str"/>
+      <x:c r="E5" s="12" t="str">
+        <x:v>citation_marker</x:v>
+      </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>Model name</x:v>
+        <x:v>Cách map</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>citation_marker/llm_mapping/manual_mapping</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>model_name</x:v>
+        <x:v>citation_marker</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>ML</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>prompt_version</x:v>
+        <x:v>mapping_confidence</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>string</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str">
-        <x:v>Prompt version</x:v>
+        <x:v>Độ tin cậy</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
-        <x:v>Not empty</x:v>
+        <x:v>0.00-1.00</x:v>
       </x:c>
       <x:c r="H6" s="12" t="str">
-        <x:v>pre_score_v1</x:v>
+        <x:v>0.90</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>ML/BA</x:v>
+        <x:v>Backend</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="str">
-        <x:v>sf</x:v>
+        <x:v>is_primary_source</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>decimal</x:v>
+        <x:v>boolean</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str"/>
-      <x:c r="E7" s="12" t="str"/>
+      <x:c r="E7" s="12" t="str">
+        <x:v>false</x:v>
+      </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Source Faithfulness</x:v>
+        <x:v>Source chính?</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
+        <x:v>true/false</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>0.85</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>ML</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="12" t="str">
-        <x:v>sc</x:v>
-      </x:c>
-      <x:c r="B8" s="12" t="str">
-        <x:v>decimal</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="str"/>
-      <x:c r="E8" s="12" t="str"/>
-      <x:c r="F8" s="12" t="str">
-        <x:v>Source Coverage</x:v>
-      </x:c>
-      <x:c r="G8" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
-      </x:c>
-      <x:c r="H8" s="12" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="I8" s="12" t="str">
-        <x:v>ML</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="12" t="str">
-        <x:v>hr</x:v>
-      </x:c>
-      <x:c r="B9" s="12" t="str">
-        <x:v>decimal</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="str"/>
-      <x:c r="E9" s="12" t="str"/>
-      <x:c r="F9" s="12" t="str">
-        <x:v>Hallucination Rate / No hallucination score</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
-      </x:c>
-      <x:c r="H9" s="12" t="str">
-        <x:v>0.90</x:v>
-      </x:c>
-      <x:c r="I9" s="12" t="str">
-        <x:v>ML</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="12" t="str">
-        <x:v>sq</x:v>
-      </x:c>
-      <x:c r="B10" s="12" t="str">
-        <x:v>decimal</x:v>
-      </x:c>
-      <x:c r="C10" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="str"/>
-      <x:c r="E10" s="12" t="str"/>
-      <x:c r="F10" s="12" t="str">
-        <x:v>Source Quality</x:v>
-      </x:c>
-      <x:c r="G10" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="str">
-        <x:v>0.80</x:v>
-      </x:c>
-      <x:c r="I10" s="12" t="str">
-        <x:v>ML</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="12" t="str">
-        <x:v>rel</x:v>
-      </x:c>
-      <x:c r="B11" s="12" t="str">
-        <x:v>decimal</x:v>
-      </x:c>
-      <x:c r="C11" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="str"/>
-      <x:c r="E11" s="12" t="str"/>
-      <x:c r="F11" s="12" t="str">
-        <x:v>Relevance</x:v>
-      </x:c>
-      <x:c r="G11" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
-      </x:c>
-      <x:c r="H11" s="12" t="str">
-        <x:v>0.88</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="str">
-        <x:v>ML</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="12" t="str">
-        <x:v>comp</x:v>
-      </x:c>
-      <x:c r="B12" s="12" t="str">
-        <x:v>decimal</x:v>
-      </x:c>
-      <x:c r="C12" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="str"/>
-      <x:c r="E12" s="12" t="str"/>
-      <x:c r="F12" s="12" t="str">
-        <x:v>Completeness</x:v>
-      </x:c>
-      <x:c r="G12" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="str">
-        <x:v>0.70</x:v>
-      </x:c>
-      <x:c r="I12" s="12" t="str">
-        <x:v>ML</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="12" t="str">
-        <x:v>composite_score</x:v>
-      </x:c>
-      <x:c r="B13" s="12" t="str">
-        <x:v>decimal</x:v>
-      </x:c>
-      <x:c r="C13" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="str"/>
-      <x:c r="E13" s="12" t="str"/>
-      <x:c r="F13" s="12" t="str">
-        <x:v>Composite score</x:v>
-      </x:c>
-      <x:c r="G13" s="12" t="str">
-        <x:v>0.00-1.00</x:v>
-      </x:c>
-      <x:c r="H13" s="12" t="str">
-        <x:v>0.81</x:v>
-      </x:c>
-      <x:c r="I13" s="12" t="str">
-        <x:v>Backend</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="12" t="str">
-        <x:v>rationale_json</x:v>
-      </x:c>
-      <x:c r="B14" s="12" t="str">
-        <x:v>json</x:v>
-      </x:c>
-      <x:c r="C14" s="12" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="str"/>
-      <x:c r="E14" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="F14" s="12" t="str">
-        <x:v>Rationale theo dimension</x:v>
-      </x:c>
-      <x:c r="G14" s="12" t="str">
-        <x:v>Valid JSON</x:v>
-      </x:c>
-      <x:c r="H14" s="12" t="str">
-        <x:v>{}</x:v>
-      </x:c>
-      <x:c r="I14" s="12" t="str">
-        <x:v>ML</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="12" t="str">
-        <x:v>created_at</x:v>
-      </x:c>
-      <x:c r="B15" s="12" t="str">
-        <x:v>datetime</x:v>
-      </x:c>
-      <x:c r="C15" s="12" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="str"/>
-      <x:c r="E15" s="12" t="str">
-        <x:v>now</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="str">
-        <x:v>Thời điểm tạo</x:v>
-      </x:c>
-      <x:c r="G15" s="12" t="str">
-        <x:v>ISO datetime</x:v>
-      </x:c>
-      <x:c r="H15" s="12" t="n">
-        <x:v>46177.375</x:v>
-      </x:c>
-      <x:c r="I15" s="12" t="str">
         <x:v>Backend</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9dedb6697504333"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd99d9bc85f0c4bb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>